--- a/data/turnos.xlsx
+++ b/data/turnos.xlsx
@@ -35,8 +35,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
   <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="201" formatCode="$ #,##0"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="$ #,##0"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -752,7 +752,7 @@
         <v>09:00-12:00</v>
       </c>
       <c r="D14" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E14" t="str">
         <v>Evento corporativo</v>
@@ -2848,16 +2848,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B1000"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2929,9 +2929,9 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B1000"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/turnos.xlsx
+++ b/data/turnos.xlsx
@@ -544,7 +544,7 @@
         <v>13:00-16:00</v>
       </c>
       <c r="D6" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E6" t="str">
         <v>Reunión privada</v>
@@ -622,7 +622,7 @@
         <v>13:00-16:00</v>
       </c>
       <c r="D9" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E9" t="str">
         <v>Reunión privada</v>
@@ -1064,7 +1064,7 @@
         <v>09:00-12:00</v>
       </c>
       <c r="D26" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E26" t="str">
         <v>Evento corporativo</v>
@@ -1168,7 +1168,7 @@
         <v>13:00-16:00</v>
       </c>
       <c r="D30" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E30" t="str">
         <v>Reunión privada</v>
@@ -1324,7 +1324,7 @@
         <v>13:00-16:00</v>
       </c>
       <c r="D36" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E36" t="str">
         <v>Reunión privada</v>
@@ -1454,7 +1454,7 @@
         <v>09:00-12:00</v>
       </c>
       <c r="D41" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E41" t="str">
         <v>Evento corporativo</v>
@@ -1766,7 +1766,7 @@
         <v>09:00-12:00</v>
       </c>
       <c r="D53" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E53" t="str">
         <v>Evento corporativo</v>
@@ -2052,7 +2052,7 @@
         <v>17:00-20:00</v>
       </c>
       <c r="D64" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E64" t="str">
         <v>Coffee break storming</v>
@@ -2130,7 +2130,7 @@
         <v>17:00-20:00</v>
       </c>
       <c r="D67" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E67" t="str">
         <v>Coffee break storming</v>
@@ -2468,7 +2468,7 @@
         <v>09:00-12:00</v>
       </c>
       <c r="D80" t="str">
-        <v>Libre</v>
+        <v>Ocupado</v>
       </c>
       <c r="E80" t="str">
         <v>Evento corporativo</v>
